--- a/enhancements/test-files/01_ARR_pc0101_2026_JanJun.xlsx
+++ b/enhancements/test-files/01_ARR_pc0101_2026_JanJun.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -432,6 +432,13 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +487,41 @@
           <t>Transaction Effective Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>MarketProvider</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Detail</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>GrossCommissionAmount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CommissionPct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionAmount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionPct</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -492,12 +534,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Global Assurance Corp</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -506,16 +548,41 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>23621.26</v>
+        <v>23791.47</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>46009</v>
+        <v>45953</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>46022</v>
+        <v>46019</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>2854.98</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1655.89</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0696</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1199.09</v>
       </c>
     </row>
     <row r="3">
@@ -529,12 +596,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>Liberty Mutual</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Metro Agency Group</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -543,16 +610,41 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2603.19</v>
+        <v>24693.43</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46026</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>45896</v>
+        <v>45738</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46026</v>
+        <v>46025</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>2963.21</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1214.92</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.0492</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1748.29</v>
       </c>
     </row>
     <row r="4">
@@ -566,12 +658,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>Liberty Mutual</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -580,16 +672,41 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7212.4</v>
+        <v>12839.47</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46029</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45897</v>
+        <v>45904</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>46028</v>
+        <v>46026</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1540.74</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N4" t="n">
+        <v>708.74</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="P4" t="n">
+        <v>832</v>
       </c>
     </row>
     <row r="5">
@@ -603,12 +720,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -617,16 +734,41 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>17898.97</v>
+        <v>7224.3</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46032</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>45808</v>
+        <v>45927</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46028</v>
+        <v>46032</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>866.92</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>554.83</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.07679999999999999</v>
+      </c>
+      <c r="P5" t="n">
+        <v>312.09</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +787,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -654,16 +796,41 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4772.26</v>
+        <v>5334.88</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46035</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>45788</v>
+        <v>46021</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46033</v>
+        <v>46031</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>640.1900000000001</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>390.52</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.0732</v>
+      </c>
+      <c r="P6" t="n">
+        <v>249.67</v>
       </c>
     </row>
     <row r="7">
@@ -682,7 +849,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -691,16 +858,41 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>13268.38</v>
+        <v>14816.6</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>46021</v>
+        <v>45758</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46053</v>
+        <v>46050</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1777.99</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N7" t="n">
+        <v>906.77</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="P7" t="n">
+        <v>871.22</v>
       </c>
     </row>
     <row r="8">
@@ -714,12 +906,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -728,16 +920,41 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>4438.98</v>
+        <v>15366.77</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>45921</v>
+        <v>45819</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46052</v>
+        <v>46054</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1844.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N8" t="n">
+        <v>922</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P8" t="n">
+        <v>922</v>
       </c>
     </row>
     <row r="9">
@@ -751,12 +968,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Apex Insurance Brokers</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -765,16 +982,41 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>16470.88</v>
+        <v>22145.95</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46060</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>46046</v>
+        <v>45805</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>46056</v>
+        <v>46060</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>2657.51</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1567.93</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1089.58</v>
       </c>
     </row>
     <row r="10">
@@ -793,7 +1035,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Metro Agency Group</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -802,16 +1044,41 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>14816.6</v>
+        <v>1770.81</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46063</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>45869</v>
+        <v>46037</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46063</v>
+        <v>46059</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N10" t="n">
+        <v>146.62</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="P10" t="n">
+        <v>65.88</v>
       </c>
     </row>
     <row r="11">
@@ -825,12 +1092,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -839,16 +1106,41 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>14352.99</v>
+        <v>5609.72</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>45790</v>
+        <v>46053</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>46065</v>
+        <v>46063</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>673.17</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N11" t="n">
+        <v>350.05</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="P11" t="n">
+        <v>323.12</v>
       </c>
     </row>
     <row r="12">
@@ -862,12 +1154,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -876,16 +1168,41 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3013.92</v>
+        <v>8263.790000000001</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>45815</v>
+        <v>45982</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>46078</v>
+        <v>46080</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>991.65</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N12" t="n">
+        <v>634.66</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.07679999999999999</v>
+      </c>
+      <c r="P12" t="n">
+        <v>356.99</v>
       </c>
     </row>
     <row r="13">
@@ -904,7 +1221,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -913,16 +1230,41 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>14735.71</v>
+        <v>13773.64</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>46085</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>45981</v>
+        <v>45808</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>46084</v>
+        <v>46081</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1652.84</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1140.46</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="P13" t="n">
+        <v>512.38</v>
       </c>
     </row>
     <row r="14">
@@ -936,12 +1278,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Metro Agency Group</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -950,16 +1292,41 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>17847.98</v>
+        <v>4847.84</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46088</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>46030</v>
+        <v>45925</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>46086</v>
+        <v>46088</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>581.74</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N14" t="n">
+        <v>267.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0552</v>
+      </c>
+      <c r="P14" t="n">
+        <v>314.14</v>
       </c>
     </row>
     <row r="15">
@@ -973,12 +1340,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -987,17 +1354,42 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>18689.42</v>
+        <v>24500.03</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46091</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>45966</v>
+        <v>45810</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>46089</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>2940</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1470</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1470</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1010,12 +1402,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>Liberty Mutual</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1024,16 +1416,41 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>11620.76</v>
+        <v>5756.08</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>45805</v>
+        <v>45860</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>46091</v>
+        <v>46092</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>690.73</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N16" t="n">
+        <v>352.27</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.0612</v>
+      </c>
+      <c r="P16" t="n">
+        <v>338.46</v>
       </c>
     </row>
     <row r="17">
@@ -1047,12 +1464,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Zenith Insurance Group</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1061,16 +1478,41 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>10813.77</v>
+        <v>7778.16</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>46031</v>
+        <v>45991</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>46113</v>
+        <v>46112</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>933.38</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N17" t="n">
+        <v>448.02</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.0576</v>
+      </c>
+      <c r="P17" t="n">
+        <v>485.36</v>
       </c>
     </row>
     <row r="18">
@@ -1084,12 +1526,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1098,16 +1540,41 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>22951.91</v>
+        <v>5314.44</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>46116</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>46103</v>
+        <v>46056</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>46113</v>
+        <v>46116</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>637.73</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N18" t="n">
+        <v>401.77</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.0756</v>
+      </c>
+      <c r="P18" t="n">
+        <v>235.96</v>
       </c>
     </row>
     <row r="19">
@@ -1121,12 +1588,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1135,16 +1602,41 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>8263.790000000001</v>
+        <v>21870.44</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46119</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>45924</v>
+        <v>45914</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>46117</v>
+        <v>46119</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>2624.45</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1233.49</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.0564</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1390.96</v>
       </c>
     </row>
     <row r="20">
@@ -1158,12 +1650,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Apex Insurance Brokers</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1172,16 +1664,41 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>22432.64</v>
+        <v>9551.799999999999</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46122</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>46008</v>
+        <v>46100</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>46120</v>
+        <v>46118</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1146.22</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N20" t="n">
+        <v>630.42</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="P20" t="n">
+        <v>515.8</v>
       </c>
     </row>
     <row r="21">
@@ -1195,12 +1712,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>Liberty Mutual</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1209,17 +1726,42 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>10553.79</v>
+        <v>16396.09</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46125</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>45848</v>
+        <v>46060</v>
       </c>
       <c r="I21" s="2" t="n">
         <v>46121</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1967.53</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N21" t="n">
+        <v>846.04</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1121.49</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1232,12 +1774,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Coastal Risk Advisors</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1246,16 +1788,41 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>11130.83</v>
+        <v>23350.39</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>45873</v>
+        <v>46127</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>46143</v>
+        <v>46141</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>2802.05</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1513.11</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1288.94</v>
       </c>
     </row>
     <row r="23">
@@ -1269,12 +1836,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Liberty Mutual</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Apex Insurance Brokers</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1283,17 +1850,42 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>4528.79</v>
+        <v>20889.17</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>45987</v>
+        <v>46076</v>
       </c>
       <c r="I23" s="2" t="n">
         <v>46141</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>2506.7</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1027.75</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.0492</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1478.95</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1306,12 +1898,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Global Assurance Corp</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Pinnacle Agency Partners</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1320,16 +1912,41 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>24386.95</v>
+        <v>16782.44</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46149</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>45880</v>
+        <v>45883</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>46144</v>
+        <v>46145</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>2013.89</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N24" t="n">
+        <v>865.97</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.0516</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1147.92</v>
       </c>
     </row>
     <row r="25">
@@ -1343,7 +1960,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Liberty Mutual</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1357,16 +1974,41 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>8463.74</v>
+        <v>20649.53</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>46152</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>45854</v>
+        <v>46080</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>46151</v>
+        <v>46152</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>2477.94</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1412.43</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.0684</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1065.51</v>
       </c>
     </row>
     <row r="26">
@@ -1394,17 +2036,42 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>16477.62</v>
+        <v>13166.51</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>46155</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>46080</v>
+        <v>46035</v>
       </c>
       <c r="I26" s="2" t="n">
         <v>46153</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1579.98</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N26" t="n">
+        <v>932.1900000000001</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.0708</v>
+      </c>
+      <c r="P26" t="n">
+        <v>647.79</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1417,7 +2084,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1431,16 +2098,41 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>22722.92</v>
+        <v>22874.38</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>45939</v>
+        <v>45927</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>46174</v>
+        <v>46173</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>2744.93</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1646.96</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1097.97</v>
       </c>
     </row>
     <row r="28">
@@ -1454,12 +2146,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1468,16 +2160,41 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>8128</v>
+        <v>6236.83</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>46177</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>45884</v>
+        <v>45909</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>46174</v>
+        <v>46177</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>748.42</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N28" t="n">
+        <v>389.18</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="P28" t="n">
+        <v>359.24</v>
       </c>
     </row>
     <row r="29">
@@ -1491,12 +2208,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1505,16 +2222,41 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>10809.79</v>
+        <v>22780.14</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>46180</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>46052</v>
+        <v>46019</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>46176</v>
+        <v>46180</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>2733.62</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1339.47</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1394.15</v>
       </c>
     </row>
     <row r="30">
@@ -1533,7 +2275,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Apex Insurance Brokers</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1542,16 +2284,41 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>20120.11</v>
+        <v>5105.33</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>46183</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>45932</v>
+        <v>46164</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>46182</v>
+        <v>46180</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>612.64</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N30" t="n">
+        <v>275.69</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="P30" t="n">
+        <v>336.95</v>
       </c>
     </row>
     <row r="31">
@@ -1565,7 +2332,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1579,16 +2346,41 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>16889.89</v>
+        <v>8118.02</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>46186</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>46168</v>
+        <v>46055</v>
       </c>
       <c r="I31" s="2" t="n">
         <v>46186</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Cancellation</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>974.16</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N31" t="n">
+        <v>399.41</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.0492</v>
+      </c>
+      <c r="P31" t="n">
+        <v>574.75</v>
       </c>
     </row>
   </sheetData>
